--- a/imports/templates/TemplateColumns2Models.xlsx
+++ b/imports/templates/TemplateColumns2Models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lg10/Workspace/git/fork/omicspred_backend/imports/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE34ED7-ACC5-DD4B-BAEA-2176AB7DCAAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D351DC9-534F-3844-B523-C0AB0B42D401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40460" yWindow="2260" windowWidth="31480" windowHeight="15820" activeTab="1" xr2:uid="{CA282B8C-A8A2-504D-820E-00F8CA4B8AF2}"/>
   </bookViews>
@@ -1901,7 +1901,7 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>45726</v>
+        <v>45737</v>
       </c>
     </row>
   </sheetData>

--- a/imports/templates/TemplateColumns2Models.xlsx
+++ b/imports/templates/TemplateColumns2Models.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lg10/Workspace/git/fork/omicspred_backend/imports/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D351DC9-534F-3844-B523-C0AB0B42D401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D40DD64-9D3E-4745-A4F7-49E7B132B9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40460" yWindow="2260" windowWidth="31480" windowHeight="15820" activeTab="1" xr2:uid="{CA282B8C-A8A2-504D-820E-00F8CA4B8AF2}"/>
+    <workbookView xWindow="36720" yWindow="2820" windowWidth="31480" windowHeight="15820" activeTab="1" xr2:uid="{CA282B8C-A8A2-504D-820E-00F8CA4B8AF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Version" sheetId="1" r:id="rId1"/>
@@ -988,38 +988,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Additional validation performance metrics/details </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(multiple columns can be applied)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">Curation Notes
 </t>
     </r>
@@ -1324,8 +1292,44 @@
     </r>
   </si>
   <si>
-    <t>Study Stage
-(Variant associations / Score development / Validation)</t>
+    <r>
+      <t xml:space="preserve">Additional validation performance metrics/details </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(multiple columns can be applied)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Study Stage
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Variant associations / Score development / Validation)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2000,7 +2004,7 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
         <v>30</v>
@@ -2034,7 +2038,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" t="s">
         <v>31</v>
@@ -2220,7 +2224,7 @@
         <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
         <v>14</v>
@@ -2243,7 +2247,7 @@
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2260,7 +2264,7 @@
         <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2274,7 +2278,7 @@
         <v>42</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
         <v>14</v>
@@ -2291,7 +2295,7 @@
         <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E20" t="s">
         <v>14</v>
@@ -2305,10 +2309,10 @@
         <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s">
         <v>37</v>
@@ -2325,13 +2329,13 @@
         <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s">
         <v>15</v>
@@ -2345,13 +2349,13 @@
         <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" t="s">
         <v>72</v>
-      </c>
-      <c r="E23" t="s">
-        <v>73</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
@@ -2365,10 +2369,10 @@
         <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E24" t="s">
         <v>14</v>
@@ -2385,10 +2389,10 @@
         <v>51</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E25" t="s">
         <v>14</v>
@@ -2402,10 +2406,10 @@
         <v>52</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E26" t="s">
         <v>14</v>
@@ -2419,10 +2423,10 @@
         <v>53</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E27" t="s">
         <v>14</v>
@@ -2439,7 +2443,7 @@
         <v>42</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E28" t="s">
         <v>14</v>
@@ -2456,7 +2460,7 @@
         <v>42</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E29" t="s">
         <v>14</v>
@@ -2470,10 +2474,10 @@
         <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E30" t="s">
         <v>14</v>
@@ -2490,10 +2494,10 @@
         <v>57</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E31" t="s">
         <v>14</v>
@@ -2507,10 +2511,10 @@
         <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D32" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E32" t="s">
         <v>14</v>
@@ -2524,13 +2528,13 @@
         <v>59</v>
       </c>
       <c r="C33" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" t="s">
         <v>82</v>
       </c>
-      <c r="D33" t="s">
-        <v>83</v>
-      </c>
       <c r="E33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F33" t="s">
         <v>15</v>
@@ -2544,13 +2548,13 @@
         <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="17" x14ac:dyDescent="0.2">
@@ -2561,13 +2565,13 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" t="s">
         <v>82</v>
       </c>
-      <c r="D35" t="s">
-        <v>83</v>
-      </c>
       <c r="E35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F35" t="s">
         <v>15</v>
@@ -2581,13 +2585,13 @@
         <v>60</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2595,16 +2599,16 @@
         <v>39</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="C37" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" t="s">
         <v>82</v>
       </c>
-      <c r="D37" t="s">
-        <v>83</v>
-      </c>
       <c r="E37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2612,13 +2616,13 @@
         <v>39</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>42</v>
       </c>
       <c r="D38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E38" t="s">
         <v>14</v>
@@ -2627,16 +2631,16 @@
     </row>
     <row r="39" spans="1:7" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="24" t="s">
-        <v>86</v>
-      </c>
       <c r="C39" t="s">
+        <v>88</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>89</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>90</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>14</v>
@@ -2647,16 +2651,16 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E40" t="s">
         <v>14</v>
@@ -2664,16 +2668,16 @@
     </row>
     <row r="41" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B41" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>89</v>
-      </c>
       <c r="D41" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E41" t="s">
         <v>14</v>
@@ -2682,16 +2686,16 @@
     </row>
     <row r="42" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A42" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" t="s">
         <v>93</v>
       </c>
-      <c r="B42" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="C42" t="s">
-        <v>94</v>
-      </c>
       <c r="D42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E42" s="11" t="s">
         <v>37</v>
@@ -2700,16 +2704,16 @@
     </row>
     <row r="43" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" t="s">
         <v>93</v>
       </c>
-      <c r="B43" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>94</v>
-      </c>
-      <c r="D43" t="s">
-        <v>95</v>
       </c>
       <c r="E43" t="s">
         <v>14</v>
@@ -2720,16 +2724,16 @@
     </row>
     <row r="44" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>92</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" t="s">
         <v>93</v>
       </c>
-      <c r="B44" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="C44" t="s">
-        <v>94</v>
-      </c>
       <c r="D44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E44" t="s">
         <v>14</v>
@@ -2740,16 +2744,16 @@
     </row>
     <row r="45" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" t="s">
         <v>93</v>
       </c>
-      <c r="B45" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="C45" t="s">
-        <v>94</v>
-      </c>
       <c r="D45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E45" t="s">
         <v>14</v>
@@ -2757,16 +2761,16 @@
     </row>
     <row r="46" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C46" t="s">
         <v>93</v>
       </c>
-      <c r="B46" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="C46" t="s">
-        <v>94</v>
-      </c>
       <c r="D46" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E46" t="s">
         <v>14</v>
@@ -2777,24 +2781,24 @@
     </row>
     <row r="47" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" t="s">
         <v>93</v>
-      </c>
-      <c r="B47" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="C47" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" t="s">
         <v>93</v>
-      </c>
-      <c r="B48" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="C48" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
